--- a/MavenBook/src/test/resources/EstimateData.xlsx
+++ b/MavenBook/src/test/resources/EstimateData.xlsx
@@ -4,18 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14040" windowHeight="2175"/>
   </bookViews>
   <sheets>
     <sheet name="EstimateHeader" sheetId="1" r:id="rId1"/>
     <sheet name="EstimateItems" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>Customer Name</t>
   </si>
@@ -35,27 +35,15 @@
     <t>Sales Person</t>
   </si>
   <si>
-    <t>Sales P1</t>
-  </si>
-  <si>
     <t>Estimate Date</t>
   </si>
   <si>
     <t>Expiry Date</t>
   </si>
   <si>
-    <t>Subinm</t>
-  </si>
-  <si>
-    <t>Red Pen</t>
-  </si>
-  <si>
     <t>Test Automation</t>
   </si>
   <si>
-    <t>30-12-2025</t>
-  </si>
-  <si>
     <t>Tax</t>
   </si>
   <si>
@@ -77,27 +65,9 @@
     <t>Save As</t>
   </si>
   <si>
-    <t>SAVE AND APPROVE</t>
-  </si>
-  <si>
     <t>Inclusive</t>
   </si>
   <si>
-    <t>26122025</t>
-  </si>
-  <si>
-    <t>26-12-2025</t>
-  </si>
-  <si>
-    <t>Automated one</t>
-  </si>
-  <si>
-    <t>Straberry</t>
-  </si>
-  <si>
-    <t>25-12-2025</t>
-  </si>
-  <si>
     <t>notex</t>
   </si>
   <si>
@@ -110,32 +80,41 @@
     <t>amount</t>
   </si>
   <si>
-    <t>Black Pen</t>
-  </si>
-  <si>
-    <t>Banana</t>
-  </si>
-  <si>
-    <t>Orange</t>
-  </si>
-  <si>
-    <t>Pear</t>
-  </si>
-  <si>
-    <t>SAVE AND SUBMIT</t>
-  </si>
-  <si>
     <t>Price List</t>
   </si>
   <si>
-    <t>special price</t>
+    <t>Customer 2</t>
+  </si>
+  <si>
+    <t>Customer 1</t>
+  </si>
+  <si>
+    <t>Item 1</t>
+  </si>
+  <si>
+    <t>Item 2</t>
+  </si>
+  <si>
+    <t>Item 3</t>
+  </si>
+  <si>
+    <t>SAVE AS DRAFT</t>
+  </si>
+  <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
+    <t>1234</t>
+  </si>
+  <si>
+    <t>1235</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +149,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1976D2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -191,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -216,6 +207,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,10 +536,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
@@ -555,86 +548,73 @@
         <v>4</v>
       </c>
       <c r="G1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>17</v>
-      </c>
       <c r="I1" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>23</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>26</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="H3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -768,7 +748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
@@ -788,99 +768,85 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="A2" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>24</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>34</v>
+      <c r="A3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
+      <c r="A4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
+      <c r="A5" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
+      <c r="A6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7">
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6">
         <v>12</v>
       </c>
     </row>

--- a/MavenBook/src/test/resources/EstimateData.xlsx
+++ b/MavenBook/src/test/resources/EstimateData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14040" windowHeight="2175"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22005" windowHeight="10740"/>
   </bookViews>
   <sheets>
     <sheet name="EstimateHeader" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="43">
   <si>
     <t>Customer Name</t>
   </si>
@@ -53,61 +53,97 @@
     <t>Discount</t>
   </si>
   <si>
+    <t>Customer Notes</t>
+  </si>
+  <si>
+    <t>Terms And Conditions</t>
+  </si>
+  <si>
+    <t>Save As</t>
+  </si>
+  <si>
+    <t>Inclusive</t>
+  </si>
+  <si>
+    <t>notex</t>
+  </si>
+  <si>
+    <t>termsx</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Price List</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Service 1</t>
+  </si>
+  <si>
     <t>Exclusive</t>
   </si>
   <si>
-    <t>Customer Notes</t>
-  </si>
-  <si>
-    <t>Terms And Conditions</t>
-  </si>
-  <si>
-    <t>Save As</t>
-  </si>
-  <si>
-    <t>Inclusive</t>
-  </si>
-  <si>
-    <t>notex</t>
-  </si>
-  <si>
-    <t>termsx</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>Price List</t>
-  </si>
-  <si>
-    <t>Customer 2</t>
-  </si>
-  <si>
-    <t>Customer 1</t>
-  </si>
-  <si>
-    <t>Item 1</t>
-  </si>
-  <si>
-    <t>Item 2</t>
-  </si>
-  <si>
-    <t>Item 3</t>
-  </si>
-  <si>
-    <t>SAVE AS DRAFT</t>
-  </si>
-  <si>
-    <t>31-03-2026</t>
-  </si>
-  <si>
-    <t>1234</t>
-  </si>
-  <si>
-    <t>1235</t>
+    <t>Vat Reg Customer</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>120826-1</t>
+  </si>
+  <si>
+    <t>120826-2</t>
+  </si>
+  <si>
+    <t>CDName</t>
+  </si>
+  <si>
+    <t>120826-3</t>
+  </si>
+  <si>
+    <t>120826-4</t>
+  </si>
+  <si>
+    <t>Mr Abel Patriarch</t>
+  </si>
+  <si>
+    <t>120826-5</t>
+  </si>
+  <si>
+    <t>120826-6</t>
+  </si>
+  <si>
+    <t>Non GCC Customer OMR</t>
+  </si>
+  <si>
+    <t>120826-7</t>
+  </si>
+  <si>
+    <t>120826-8</t>
+  </si>
+  <si>
+    <t>120826-9</t>
+  </si>
+  <si>
+    <t>120826-10</t>
+  </si>
+  <si>
+    <t>30-08-2026</t>
+  </si>
+  <si>
+    <t>SAVE AND APPROVE</t>
+  </si>
+  <si>
+    <t>Non inv 1</t>
+  </si>
+  <si>
+    <t>Avokado</t>
   </si>
 </sst>
 </file>
@@ -151,15 +187,16 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF1976D2"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,7 +207,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -178,37 +215,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="1" customWidth="1"/>
@@ -528,126 +593,310 @@
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>21</v>
+      <c r="K1" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>27</v>
+      <c r="J2" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>27</v>
+      <c r="J3" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
+      <c r="A6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E6" s="1"/>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
+      <c r="A7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E7" s="1"/>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E8" s="1"/>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E9" s="1"/>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E10" s="1"/>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="E11" s="1"/>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
@@ -712,43 +961,19 @@
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
       <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="1"/>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="1"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="1"/>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="1"/>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="1"/>
-      <c r="E33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="E4:E33" numberStoredAsText="1"/>
+    <ignoredError sqref="E6:E27" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" style="1" customWidth="1"/>
@@ -757,98 +982,342 @@
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="6">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="6">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C5" s="6">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E2">
+      <c r="E7" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C9" s="6">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="19">
+        <v>5</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="19">
+        <v>5</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="19">
+        <v>5</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="19">
+        <v>5</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="19">
+        <v>5</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="19">
+        <v>5</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="19">
+        <v>5</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="19">
+        <v>5</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="B18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="19">
+        <v>5</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="19">
+        <v>5</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="19">
+        <v>5</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6">
-        <v>12</v>
-      </c>
+      <c r="C21" s="19">
+        <v>5</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
